--- a/Palmares_Football_FM26_Complet_V3.xlsx
+++ b/Palmares_Football_FM26_Complet_V3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utilisateur\Documents\liste champions map\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{728FCB51-0E68-4ACF-AED6-0430BFC42E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E714EFC4-1E58-4D52-AEF3-4FC64394AA13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="17" activeTab="25" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2554,7 +2554,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2605,13 +2605,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor rgb="FFFF9900"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFFF9900"/>
         <bgColor rgb="FF00B050"/>
       </patternFill>
     </fill>
@@ -2658,7 +2652,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2746,21 +2740,17 @@
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF9900"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -6928,19 +6918,19 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="28" t="s">
+      <c r="A10" s="19" t="s">
         <v>355</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="19" t="s">
         <v>347</v>
       </c>
-      <c r="C10" s="29">
-        <v>1</v>
-      </c>
-      <c r="D10" s="30">
+      <c r="C10" s="20">
+        <v>1</v>
+      </c>
+      <c r="D10" s="21">
         <v>1998</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="21">
         <v>1</v>
       </c>
     </row>
@@ -7082,6 +7072,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7574,19 +7565,19 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="31" t="s">
+      <c r="A12" s="28" t="s">
         <v>392</v>
       </c>
-      <c r="B12" s="31" t="s">
+      <c r="B12" s="28" t="s">
         <v>393</v>
       </c>
-      <c r="C12" s="32">
+      <c r="C12" s="29">
         <v>3</v>
       </c>
-      <c r="D12" s="33">
+      <c r="D12" s="30">
         <v>1938</v>
       </c>
-      <c r="E12" s="33">
+      <c r="E12" s="30">
         <v>2</v>
       </c>
     </row>

--- a/Palmares_Football_FM26_Complet_V3.xlsx
+++ b/Palmares_Football_FM26_Complet_V3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utilisateur\Documents\liste champions map\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5DC7552-2F31-450A-88F6-02F8724FD52B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DD34C89-23AB-4BB2-8A7B-7F3001FF498B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="276" windowWidth="20376" windowHeight="12096" firstSheet="26" activeTab="33" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="276" windowWidth="20376" windowHeight="12096" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Finalistes malheureux" sheetId="1" r:id="rId1"/>
@@ -2746,6 +2746,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF2072B8"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -13816,6 +13821,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/Palmares_Football_FM26_Complet_V3.xlsx
+++ b/Palmares_Football_FM26_Complet_V3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utilisateur\Documents\liste champions map\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD8E43F9-BC3A-4C2F-B283-643746A89C8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66216EBE-19C3-41B6-BE2F-0E74F501219C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Finalistes malheureux" sheetId="1" r:id="rId1"/>
@@ -95,7 +95,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1837" uniqueCount="812">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1837" uniqueCount="811">
   <si>
     <t>Nom de l'équipe</t>
   </si>
@@ -2528,9 +2528,6 @@
   </si>
   <si>
     <t>Progreso</t>
-  </si>
-  <si>
-    <t>FCSB /  Steaua Bucarest</t>
   </si>
 </sst>
 </file>
@@ -6935,7 +6932,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>811</v>
+        <v>701</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>38</v>

--- a/Palmares_Football_FM26_Complet_V3.xlsx
+++ b/Palmares_Football_FM26_Complet_V3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utilisateur\Documents\liste champions map\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{46A18E25-AB84-484B-9333-3EAF432AEE82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C8D8EB17-07B9-492D-B4B0-4062CC9FA274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="276" windowWidth="20376" windowHeight="12096" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
